--- a/셀픽_영업처_아기샴푸치약칫솔.xlsx
+++ b/셀픽_영업처_아기샴푸치약칫솔.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="120">
   <si>
     <t>브랜드명</t>
   </si>
@@ -82,15 +82,54 @@
     <t>궁중비책</t>
   </si>
   <si>
+    <t>제제지크</t>
+  </si>
+  <si>
+    <t>네이쳐러브메레</t>
+  </si>
+  <si>
+    <t>베이비피아</t>
+  </si>
+  <si>
+    <t>Jordankorea</t>
+  </si>
+  <si>
+    <t>덴티플</t>
+  </si>
+  <si>
+    <t>큐라덴 큐라프록스</t>
+  </si>
+  <si>
+    <t>제니튼</t>
+  </si>
+  <si>
+    <t>아가드</t>
+  </si>
+  <si>
+    <t>마미다</t>
+  </si>
+  <si>
+    <t>귀여운아기</t>
+  </si>
+  <si>
     <t>아기 샴푸</t>
   </si>
   <si>
+    <t>아기 칫솔</t>
+  </si>
+  <si>
     <t>베이비 스킨케어</t>
   </si>
   <si>
+    <t>유아 의류</t>
+  </si>
+  <si>
     <t>아기 샴푸 (웹검색)</t>
   </si>
   <si>
+    <t>아기 칫솔 (웹검색)</t>
+  </si>
+  <si>
     <t>02-856-2030</t>
   </si>
   <si>
@@ -121,6 +160,36 @@
     <t>1588-7601</t>
   </si>
   <si>
+    <t>080-628-8800</t>
+  </si>
+  <si>
+    <t>1544-2368</t>
+  </si>
+  <si>
+    <t>1566-8786</t>
+  </si>
+  <si>
+    <t>010-2845-9400</t>
+  </si>
+  <si>
+    <t>070-4524-0494</t>
+  </si>
+  <si>
+    <t>070-7771-2875</t>
+  </si>
+  <si>
+    <t>1599-8344</t>
+  </si>
+  <si>
+    <t>1877-6518</t>
+  </si>
+  <si>
+    <t>1688-8389</t>
+  </si>
+  <si>
+    <t>07080954346</t>
+  </si>
+  <si>
     <t>hello@doctornoah.net</t>
   </si>
   <si>
@@ -151,6 +220,36 @@
     <t>0to7CS@ckbiz.co.kr</t>
   </si>
   <si>
+    <t>jejejik@avent.co.kr</t>
+  </si>
+  <si>
+    <t>office@klemarang.com</t>
+  </si>
+  <si>
+    <t>jesun0911@babypia.co.kr</t>
+  </si>
+  <si>
+    <t>jenny.park@orkla.com</t>
+  </si>
+  <si>
+    <t>bom-eroom@naver.com</t>
+  </si>
+  <si>
+    <t>sales_support2@curadenkorea.com</t>
+  </si>
+  <si>
+    <t>dr_zeniton@naver.com</t>
+  </si>
+  <si>
+    <t>lipaco@daum.net</t>
+  </si>
+  <si>
+    <t>info@momida.com</t>
+  </si>
+  <si>
+    <t>prettybaby@outlook.kr</t>
+  </si>
+  <si>
     <t>662-85-00197</t>
   </si>
   <si>
@@ -181,6 +280,36 @@
     <t>220-81-76684</t>
   </si>
   <si>
+    <t>229-81-38090</t>
+  </si>
+  <si>
+    <t>141-81-36619</t>
+  </si>
+  <si>
+    <t>128-86-43179</t>
+  </si>
+  <si>
+    <t>206-86-22571</t>
+  </si>
+  <si>
+    <t>599-81-03544</t>
+  </si>
+  <si>
+    <t>151-87-01351</t>
+  </si>
+  <si>
+    <t>204-86-15773</t>
+  </si>
+  <si>
+    <t>301-81-32627</t>
+  </si>
+  <si>
+    <t>103-86-01428</t>
+  </si>
+  <si>
+    <t>122-14-65580</t>
+  </si>
+  <si>
     <t>https://doctornoah.net</t>
   </si>
   <si>
@@ -209,6 +338,36 @@
   </si>
   <si>
     <t>https://goongbe.com</t>
+  </si>
+  <si>
+    <t>https://avent.co.kr</t>
+  </si>
+  <si>
+    <t>https://naturelovemere.com</t>
+  </si>
+  <si>
+    <t>https://babypia.co.kr</t>
+  </si>
+  <si>
+    <t>https://jordankorea.co.kr</t>
+  </si>
+  <si>
+    <t>https://dentiple.kr</t>
+  </si>
+  <si>
+    <t>https://curaprox.co.kr</t>
+  </si>
+  <si>
+    <t>https://zeniton.com</t>
+  </si>
+  <si>
+    <t>https://aguardmall.com</t>
+  </si>
+  <si>
+    <t>https://momida.com</t>
+  </si>
+  <si>
+    <t>https://prettybaby.co.kr</t>
   </si>
   <si>
     <t>중간</t>
@@ -591,17 +750,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="33.7109375" customWidth="1"/>
     <col min="7" max="8" width="10.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="28.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.7109375" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" customWidth="1"/>
   </cols>
@@ -649,31 +808,31 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L2" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -681,31 +840,31 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L3" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -713,31 +872,31 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="K4" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -745,31 +904,31 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L5" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -777,31 +936,31 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L6" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -809,31 +968,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -841,31 +1000,31 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -873,31 +1032,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="K9" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L9" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -905,31 +1064,31 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="K10" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="L10" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -937,31 +1096,351 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K11" t="s">
+        <v>118</v>
+      </c>
+      <c r="L11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" t="s">
+        <v>118</v>
+      </c>
+      <c r="L12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" t="s">
+        <v>89</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" t="s">
+        <v>118</v>
+      </c>
+      <c r="L13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K15" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" t="s">
+        <v>118</v>
+      </c>
+      <c r="L17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K11" t="s">
-        <v>65</v>
-      </c>
-      <c r="L11" t="s">
-        <v>66</v>
+      <c r="F18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K18" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K19" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K20" t="s">
+        <v>118</v>
+      </c>
+      <c r="L20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K21" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -976,6 +1455,16 @@
     <hyperlink ref="J9" r:id="rId8"/>
     <hyperlink ref="J10" r:id="rId9"/>
     <hyperlink ref="J11" r:id="rId10"/>
+    <hyperlink ref="J12" r:id="rId11"/>
+    <hyperlink ref="J13" r:id="rId12"/>
+    <hyperlink ref="J14" r:id="rId13"/>
+    <hyperlink ref="J15" r:id="rId14"/>
+    <hyperlink ref="J16" r:id="rId15"/>
+    <hyperlink ref="J17" r:id="rId16"/>
+    <hyperlink ref="J18" r:id="rId17"/>
+    <hyperlink ref="J19" r:id="rId18"/>
+    <hyperlink ref="J20" r:id="rId19"/>
+    <hyperlink ref="J21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
